--- a/Pruebas calificadas/COLEGIO MIRAVALLE (IED)-1103_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO MIRAVALLE (IED)-1103_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1558,11 +1546,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -1570,7 +1554,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1811,11 +1795,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -1823,7 +1803,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2064,11 +2044,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -2076,7 +2052,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2317,11 +2293,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -2329,7 +2301,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2570,11 +2542,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -2582,7 +2550,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2823,11 +2791,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -2835,7 +2799,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3068,11 +3032,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -3080,7 +3040,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3317,11 +3277,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -3329,7 +3285,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3570,11 +3526,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -3582,7 +3534,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3819,11 +3771,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -3831,7 +3779,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4072,11 +4020,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -4084,7 +4028,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4325,11 +4269,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -4337,7 +4277,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4578,11 +4518,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -4590,7 +4526,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4831,11 +4767,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -4843,7 +4775,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5080,11 +5012,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -5092,7 +5020,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5333,11 +5261,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -5345,7 +5269,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5586,11 +5510,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -5598,7 +5518,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5839,11 +5759,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -5851,7 +5767,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6092,11 +6008,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -6104,7 +6016,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6345,11 +6257,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -6357,7 +6265,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6598,11 +6506,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -6610,7 +6514,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6851,11 +6755,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -6863,7 +6763,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7104,11 +7004,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -7116,7 +7012,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7357,11 +7253,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -7369,7 +7261,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7610,11 +7502,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -7622,7 +7510,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7863,11 +7751,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -7875,7 +7759,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8116,11 +8000,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -8128,7 +8008,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8369,11 +8249,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -8381,7 +8257,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8622,11 +8498,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -8634,7 +8506,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8875,11 +8747,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -8887,7 +8755,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9128,11 +8996,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -9140,7 +9004,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9381,11 +9245,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -9393,7 +9253,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9634,11 +9494,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -9646,7 +9502,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9887,11 +9743,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -9899,7 +9751,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10140,11 +9992,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -10152,7 +10000,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10393,11 +10241,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -10405,7 +10249,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10646,11 +10490,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -10658,7 +10498,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10899,11 +10739,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -10911,7 +10747,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11152,11 +10988,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -11164,7 +10996,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11405,11 +11237,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -11417,7 +11245,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11658,11 +11486,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -11670,7 +11494,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11911,11 +11735,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -11923,7 +11743,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12164,11 +11984,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -12176,7 +11992,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12417,11 +12233,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -12429,7 +12241,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12670,11 +12482,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -12682,7 +12490,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12923,11 +12731,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -12935,7 +12739,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13172,11 +12976,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -13184,7 +12984,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13425,11 +13225,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -13437,7 +13233,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13678,11 +13474,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -13690,7 +13482,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13931,11 +13723,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -13943,7 +13731,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14184,11 +13972,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -14196,7 +13980,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14437,11 +14221,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -14449,7 +14229,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14690,11 +14470,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -14702,7 +14478,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14943,11 +14719,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -14955,7 +14727,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15196,11 +14968,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -15208,7 +14976,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -15449,11 +15217,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -15461,7 +15225,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15702,11 +15466,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -15714,7 +15474,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -15955,11 +15715,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -15967,7 +15723,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -16208,11 +15964,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -16220,7 +15972,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -16461,11 +16213,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -16473,7 +16221,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -16714,11 +16462,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001100081</t>
@@ -16726,7 +16470,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MIRAVALLE (IED)</t>
+          <t>COLEGIO MIRAVALLE (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
